--- a/data/processed/raw_video_data.xlsx
+++ b/data/processed/raw_video_data.xlsx
@@ -543,12 +543,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IxDF</t>
+          <t>IDF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IxDF-HCI</t>
+          <t>IDF-HCI</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -579,12 +579,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IxDF</t>
+          <t>IDF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IxDF-IDU</t>
+          <t>IDF-IDU</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -615,12 +615,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IxDF</t>
+          <t>IDF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IxDF-UI</t>
+          <t>IDF-UI</t>
         </is>
       </c>
       <c r="C6" t="n">
